--- a/data/citations.xlsx
+++ b/data/citations.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8659" uniqueCount="2836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11443" uniqueCount="2837">
   <si>
     <t>title</t>
   </si>
@@ -8711,6 +8711,10 @@
   </si>
   <si>
     <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Web of Science Core Collection</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9129,7 +9133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F675"/>
+  <dimension ref="A1:G675"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="112.25" style="1" customWidth="1"/>
@@ -9139,7 +9143,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9158,8 +9162,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1213</v>
       </c>
@@ -9176,7 +9183,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>574</v>
       </c>
@@ -9196,7 +9203,7 @@
         <v>2724</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>82</v>
       </c>
@@ -9213,7 +9220,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>768</v>
       </c>
@@ -9230,7 +9237,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>252</v>
       </c>
@@ -9250,7 +9257,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>753</v>
       </c>
@@ -9270,7 +9277,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>503</v>
       </c>
@@ -9290,7 +9297,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>499</v>
       </c>
@@ -9307,7 +9314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>465</v>
       </c>
@@ -9324,7 +9331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>458</v>
       </c>
@@ -9344,7 +9351,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>392</v>
       </c>
@@ -9364,7 +9371,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>271</v>
       </c>
@@ -9381,7 +9388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>1287</v>
       </c>
@@ -9398,7 +9405,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>1668</v>
       </c>
@@ -9415,7 +9422,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>381</v>
       </c>
